--- a/corpus/xlsx/level-012/template.xlsx
+++ b/corpus/xlsx/level-012/template.xlsx
@@ -38,105 +38,105 @@
         <sz val="11"/>
         <rFont val="Calibri"/>
       </rPr>
-      <t xml:space="preserve">{{ti</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">tle}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{cust</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">omer}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{co</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">unt}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{spa</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">ced}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{ena</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">bled}}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">{{lit</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-      </rPr>
-      <t xml:space="preserve">eral}}</t>
+      <t xml:space="preserve">{d.t</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">itle}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.cus</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">tomer}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.c</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">ount}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.sp</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">aced}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.en</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">abled}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">{d.li</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+      </rPr>
+      <t xml:space="preserve">teral}</t>
     </r>
   </si>
 </sst>
